--- a/originales/respuestas/2025/01. Calificadas/bucle p15/Alcaldía Local De Rafael Uribe Uribe.xlsx
+++ b/originales/respuestas/2025/01. Calificadas/bucle p15/Alcaldía Local De Rafael Uribe Uribe.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="25629"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10913"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\LENOVO\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/apple/Downloads/IIP - Esteban/bucle p15/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{5B515C7C-0D89-498A-BD14-9FC39DA16008}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3FBD7E78-EB96-2D4B-B66A-1F0733ABF6C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{1FC750EF-E230-4B2B-9107-89A46AE1F948}"/>
+    <workbookView xWindow="0" yWindow="740" windowWidth="19420" windowHeight="10300" xr2:uid="{1FC750EF-E230-4B2B-9107-89A46AE1F948}"/>
   </bookViews>
   <sheets>
     <sheet name="Entidad" sheetId="1" r:id="rId1"/>
@@ -142,11 +142,13 @@
       <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="4">
@@ -571,9 +573,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3BBD39FA-5EB8-49D0-994C-D9C77D7F0194}">
   <sheetPr codeName="Hoja1"/>
   <dimension ref="A1:R3"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:18" ht="37.5" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:18" ht="42" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -629,7 +631,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="2" spans="1:18" ht="300" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:18" ht="306" x14ac:dyDescent="0.2">
       <c r="A2" s="4" t="s">
         <v>18</v>
       </c>
@@ -653,35 +655,35 @@
         <v>24</v>
       </c>
       <c r="I2" s="4">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="J2" s="4" t="s">
         <v>25</v>
       </c>
       <c r="K2" s="4">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="L2" s="4" t="s">
         <v>26</v>
       </c>
       <c r="M2" s="4">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="N2" s="4" t="s">
         <v>27</v>
       </c>
       <c r="O2" s="4">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="P2" s="4" t="s">
         <v>28</v>
       </c>
       <c r="Q2" s="4">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="R2" s="4"/>
     </row>
-    <row r="3" spans="1:18" ht="87.5" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:18" ht="98" x14ac:dyDescent="0.2">
       <c r="A3" s="4" t="s">
         <v>18</v>
       </c>
@@ -703,31 +705,31 @@
         <v>24</v>
       </c>
       <c r="I3" s="4">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="J3" s="4" t="s">
         <v>25</v>
       </c>
       <c r="K3" s="4">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="L3" s="4" t="s">
         <v>26</v>
       </c>
       <c r="M3" s="4">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="N3" s="4" t="s">
         <v>27</v>
       </c>
       <c r="O3" s="4">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="P3" s="4" t="s">
         <v>28</v>
       </c>
       <c r="Q3" s="4">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="R3" s="4"/>
     </row>
